--- a/artfynd/A 16786-2020 artfynd.xlsx
+++ b/artfynd/A 16786-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16786-2020 artfynd.xlsx
+++ b/artfynd/A 16786-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,230 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120552656</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91872</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>689849</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6374780</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120552675</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>689832</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6374780</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16786-2020 artfynd.xlsx
+++ b/artfynd/A 16786-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,716 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120553073</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97952</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>689833</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6374774</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120552682</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>689846</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6374782</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120553190</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>689833</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6374774</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120552638</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>689865</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6374782</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120552982</v>
+      </c>
+      <c r="B9" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>689834</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6374767</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120552620</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>689866</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6374785</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120552789</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91872</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Valdarve, Valdarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>689825</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6374804</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
